--- a/output/pdf_financials_xlsx/BRS.xlsx
+++ b/output/pdf_financials_xlsx/BRS.xlsx
@@ -1928,13 +1928,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>3.543751</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>4.07619</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.578192</v>
       </c>
     </row>
     <row r="93">
@@ -3139,7 +3139,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -3399,7 +3403,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>3.543751</v>
       </c>

--- a/output/pdf_financials_xlsx/BRS.xlsx
+++ b/output/pdf_financials_xlsx/BRS.xlsx
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.01003</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.335045</v>
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.01003</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.335045</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.01213</v>
+        <v>0.0021</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.0587</v>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">

--- a/output/pdf_financials_xlsx/BRS.xlsx
+++ b/output/pdf_financials_xlsx/BRS.xlsx
@@ -2063,13 +2063,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.022285</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.013182</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.017535</v>
       </c>
     </row>
     <row r="102">
@@ -2143,13 +2143,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.108533</v>
+        <v>0.08624800000000001</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.163086</v>
+        <v>-0.176268</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.019967</v>
+        <v>-0.037502</v>
       </c>
     </row>
     <row r="107">
@@ -3748,7 +3748,11 @@
           <t>Write-off of GST receivable</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.007439</v>
       </c>
@@ -3835,7 +3839,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>-0.029724</v>
       </c>
@@ -4634,7 +4642,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
